--- a/travel/2026-10_JIPF83/学会出席等出張許可申請書_10月16-18日_日本財政学会.xlsx
+++ b/travel/2026-10_JIPF83/学会出席等出張許可申請書_10月16-18日_日本財政学会.xlsx
@@ -196,8 +196,8 @@
   </si>
   <si>
     <t xml:space="preserve">日本財政学会 第83回大会
-自由論題にて研究報告
-報告題目：「【報告題目】」</t>
+自由論題にて研究報告（10月18日 分科会C-3「地方財政３」）
+報告題目：「地方財政レジリエンス論の理論的再構成ーフィンランドを通じた政府間財政関係論の再検討」</t>
   </si>
   <si>
     <t xml:space="preserve">〒101-8425　東京都千代田区神田神保町3-8
